--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_MBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_MBC.xlsx
@@ -933,7 +933,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -1423,7 +1427,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
@@ -2503,7 +2511,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -3225,7 +3237,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
@@ -4305,7 +4321,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
@@ -4533,7 +4553,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -5643,7 +5667,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -6123,7 +6151,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
@@ -7717,7 +7749,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
@@ -7909,7 +7945,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -8003,7 +8043,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -8391,7 +8435,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -8647,7 +8695,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -8839,7 +8891,11 @@
           <t>MBC_M._CAMERON</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322740</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>M. Cameron</t>
@@ -9031,7 +9087,11 @@
           <t>MBC_G._RODRIGUES</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>230543</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>G. Rodrigues</t>
